--- a/data/TC/result_TC.xlsx
+++ b/data/TC/result_TC.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,11 @@
           <t>챗봇 답변(한국어 번역)</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>자동 감지 언어</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -474,39 +479,10 @@
           <t>이번이 한국 첫 여행인데, 서울에서 5일 동안 K-pop과 쇼핑을 즐기고 싶어요. 어디 가면 좋을까요?</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>이번이 한국 첫 여행인데, 서울에서 5일 동안 K-pop과 쇼핑을 즐기고 싶어요. 어디 가면 좋을까요?</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>한국을 처음 방문한 여행객이 서울에서 K-pop과 쇼핑을 즐기기 좋은 곳으로 추천드리는 장소는 다음과 같습니다:
-1. **파크 하얏트 서울**
-   - **주소:** 서울 강남구 테헤란로 606
-   - **AI 요약:** 한달에 한번씩 꼭 가는 호텔로, 깔끔하고 고급스럽며 개인적 취향 중 1위로 손꼽히는 곳
-   - **주요 특징 및 후기:** 넓은 객실과 뷰, 레지던스형 호텔로 주방 및 세탁기까지 갖춰져 있어 편리하며, 서비스와 조식 등 모두 훌륭함
-2. **시그니엘 서울**
-   - **주소:** 서울 송파구 올림픽로 300 롯데월드타워 76~101층
-   - **AI 요약:** 아멕스 FHR로 묵었을 때 방이 넓고 서울시내야경이 파노라마처럼 보이는 럭셔리한 호텔
-   - **주요 특징 및 후기:** 조식, 웰컴티서비스케익 등이 훌륭하며, 높은 층에서의 뷰가 매력적이고, 라운지 샴페인바가 인기
-이 두 곳은 서울에서 럭셔리한 휴식과 쇼핑을 즐기기에 적합한 곳입니다. 특히, 파크 하얏트 서울은 깔끔하고 고급스러운 분위기와 넓은 객실, 레지던스형 호텔로서의 부가 시설이 돋보이며, 시그니엘 서울은 아름다운 뷰와 훌륭한 서비스로 럭셔리한 경험을 제공합니다. 좋은 여행이 되시길 바랍니다!</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>한국을 처음 방문한 여행객이 서울에서 K-pop과 쇼핑을 즐기기 좋은 곳으로 추천드리는 장소는 다음과 같습니다:
-1. **파크 하얏트 서울**
-   - **주소:** 서울 강남구 테헤란로 606
-   - **AI 요약:** 한달에 한번씩 꼭 가는 호텔로, 깔끔하고 고급스럽며 개인적 취향 중 1위로 손꼽히는 곳
-   - **주요 특징 및 후기:** 넓은 객실과 뷰, 레지던스형 호텔로 주방 및 세탁기까지 갖춰져 있어 편리하며, 서비스와 조식 등 모두 훌륭함
-2. **시그니엘 서울**
-   - **주소:** 서울 송파구 올림픽로 300 롯데월드타워 76~101층
-   - **AI 요약:** 아멕스 FHR로 묵었을 때 방이 넓고 서울시내야경이 파노라마처럼 보이는 럭셔리한 호텔
-   - **주요 특징 및 후기:** 조식, 웰컴티서비스케익 등이 훌륭하며, 높은 층에서의 뷰가 매력적이고, 라운지 샴페인바가 인기
-이 두 곳은 서울에서 럭셔리한 휴식과 쇼핑을 즐기기에 적합한 곳입니다. 특히, 파크 하얏트 서울은 깔끔하고 고급스러운 분위기와 넓은 객실, 레지던스형 호텔로서의 부가 시설이 돋보이며, 시그니엘 서울은 아름다운 뷰와 훌륭한 서비스로 럭셔리한 경험을 제공합니다. 좋은 여행이 되시길 바랍니다!</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -522,21 +498,10 @@
           <t>한국은 두 번째 방문인데, 제주도에서 3일 동안 자연경관과 전통문화를 느낄 수 있는 코스를 추천해 주세요.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>한국은 두 번째 방문인데, 제주도에서 3일 동안 자연경관과 전통문화를 느낄 수 있는 코스를 추천해 주세요.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>요청하신 지역에 맞는 장소를 찾지 못했습니다.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>요청하신 지역에 맞는 장소를 찾지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -552,39 +517,10 @@
           <t>부모님과 함께하는 재방문 여행으로 강원도에서 4일 동안 음식과 힐링을 하고 싶어요.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>부모님과 함께하는 재방문 여행으로 강원도에서 4일 동안 음식과 힐링을 하고 싶어요.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>알뜰한 소비와 음식, 힐링을 즐기며 부모님과 함께하는 강원도 여행을 계획 중이신 여행객을 위해 추천해 드릴 장소는 '산채촌'과 '허브나라농원'입니다.
-1. 산채촌
-- 주소: 강원특별자치도 인제군 북면 어두원길 25
-- AI 요약: 자연 경관과 시골 느낌이 물씬 풍기는 산채촌은 건강한 식사와 가족, 지인과의 모임에 적합한 곳입니다. 신선하고 담백한 음식으로 손님들을 만족시키며, 후기들에는 더덕구이와 산채정식 등이 매우 인기가 있음을 확인할 수 있습니다.
-- 주요 특징 및 후기: "산채정식 맛있어요", "능이 듬뿍 넣은 백숙 최고입니다", "김치랑 다양한 나물을 좋은 뷰에서 맛볼 수 있어요" 등 다양한 음식 후기가 있으며, 가족과 함께하는 특별한 식사로 추천합니다.
-2. 허브나라농원
-- 주소: 강원특별자치도 평창군 봉평면 흥정계곡길 225
-- AI 요약: 허브나라농원은 가성비 좋은 관광지로, 정원 구경과 시원한 계곡에서 휴식을 즐길 수 있는 곳입니다. 허브아이스크림과 허브차를 즐길 수 있는 카페도 인기가 있습니다.
-- 주요 특징 및 후기: "입장료에 비해 가성비 좋은 관광지입니다", "공기맑은 곳에서 산책하며 힐링하는 곳", "식물도 많고 꽃도 많아요" 등의 후기가 있으며, 자연 속에서 부모님과 함께 힐링하기 좋은 장소로 추천합니다.
-산채촌은 건강한 음식과 가족 모임에 적합한 분위기를 제공하며, 허브나라농원은 가성비 좋은 관광지로 힐링과 자연을 즐기기 좋은 곳입니다. 부모님과 함께하는 특별한 강원도 여행으로 즐거운 추억을 만들어보세요.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>알뜰한 소비와 음식, 힐링을 즐기며 부모님과 함께하는 강원도 여행을 계획 중이신 여행객을 위해 추천해 드릴 장소는 '산채촌'과 '허브나라농원'입니다.
-1. 산채촌
-- 주소: 강원특별자치도 인제군 북면 어두원길 25
-- AI 요약: 자연 경관과 시골 느낌이 물씬 풍기는 산채촌은 건강한 식사와 가족, 지인과의 모임에 적합한 곳입니다. 신선하고 담백한 음식으로 손님들을 만족시키며, 후기들에는 더덕구이와 산채정식 등이 매우 인기가 있음을 확인할 수 있습니다.
-- 주요 특징 및 후기: "산채정식 맛있어요", "능이 듬뿍 넣은 백숙 최고입니다", "김치랑 다양한 나물을 좋은 뷰에서 맛볼 수 있어요" 등 다양한 음식 후기가 있으며, 가족과 함께하는 특별한 식사로 추천합니다.
-2. 허브나라농원
-- 주소: 강원특별자치도 평창군 봉평면 흥정계곡길 225
-- AI 요약: 허브나라농원은 가성비 좋은 관광지로, 정원 구경과 시원한 계곡에서 휴식을 즐길 수 있는 곳입니다. 허브아이스크림과 허브차를 즐길 수 있는 카페도 인기가 있습니다.
-- 주요 특징 및 후기: "입장료에 비해 가성비 좋은 관광지입니다", "공기맑은 곳에서 산책하며 힐링하는 곳", "식물도 많고 꽃도 많아요" 등의 후기가 있으며, 자연 속에서 부모님과 함께 힐링하기 좋은 장소로 추천합니다.
-산채촌은 건강한 음식과 가족 모임에 적합한 분위기를 제공하며, 허브나라농원은 가성비 좋은 관광지로 힐링과 자연을 즐기기 좋은 곳입니다. 부모님과 함께하는 특별한 강원도 여행으로 즐거운 추억을 만들어보세요.</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -600,43 +536,10 @@
           <t>This is my first trip to Korea, I plan a 5-day stay in Seoul focused on K-pop and shopping. Where should I go?</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>이것은 한국으로의 첫 여행이며, K-Pop과 쇼핑에 중점을 둔 서울에서 5 일 체류를 계획하고 있습니다. 어디로 가야합니까?</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>한국을 처음 방문한 K-pop과 쇼핑을 즐기는 여행객에게 추천하는 장소는 '시그니엘 서울'과 '파크 하얏트 서울'입니다.
-1. **시그니엘 서울**
-   - **이름:** 시그니엘 서울
-   - **주소:** 서울 송파구 올림픽로 300 롯데월드타워 76~101층
-   - **AI 요약:** 방도 넓고 서울시내 야경이 멋진 호텔로, 조식과 서비스 훌륭함
-   - **주요 특징 및 후기:** 파노라마 야경과 훌륭한 조식으로 유명하며, 럭셔리한 분위기와 서비스를 제공합니다. 다소 비싸지만 뷰와 맛으로 보상받을 수 있습니다. 또한, 친절한 직원분들과 깔끔한 객실이 여행을 더욱 특별하게 만들어줍니다. 후기 중에는 "소중한 사람과 한번 가보시길"이라는 추천도 있습니다.
-2. **파크 하얏트 서울**
-   - **이름:** 파크 하얏트 서울
-   - **주소:** 서울 강남구 테헤란로 606
-   - **AI 요약:** 한달에 한번씩 방문하는 로비라운지가 높은 층에 위치한 럭셔리 호텔
-   - **주요 특징 및 후기:** 파크 하얏트 서울은 프라이빗한 분위기와 높은 서비스 퀄리티로 유명합니다. 특히, 시티뷰가 최고라는 평가와 친절한 직원분들이 인상적입니다. 또한, 룸서비스의 맛과 품격 또한 강조되며, 전망이 아름다운 호텔로 여행을 더욱 특별하게 만들어줍니다. 후기 중에는 "파크 하얏트가 진짜 제일 좋은 것"이라는 말도 있습니다.
-이 두 곳은 서울에서 럭셔리한 투숙 경험을 즐기면서 K-pop과 쇼핑을 즐기기에 적합한 장소로 추천드립니다. 즐거운 여행되세요!</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>한국을 처음 방문한 K-pop과 쇼핑을 즐기는 여행객에게 추천하는 장소는 '시그니엘 서울'과 '파크 하얏트 서울'입니다.
-1. **시그니엘 서울**
-   - **이름:** 시그니엘 서울
-   - **주소:** 서울 송파구 올림픽로 300 롯데월드타워 76~101층
-   - **AI 요약:** 방도 넓고 서울시내 야경이 멋진 호텔로, 조식과 서비스 훌륭함
-   - **주요 특징 및 후기:** 파노라마 야경과 훌륭한 조식으로 유명하며, 럭셔리한 분위기와 서비스를 제공합니다. 다소 비싸지만 뷰와 맛으로 보상받을 수 있습니다. 또한, 친절한 직원분들과 깔끔한 객실이 여행을 더욱 특별하게 만들어줍니다. 후기 중에는 "소중한 사람과 한번 가보시길"이라는 추천도 있습니다.
-2. **파크 하얏트 서울**
-   - **이름:** 파크 하얏트 서울
-   - **주소:** 서울 강남구 테헤란로 606
-   - **AI 요약:** 한달에 한번씩 방문하는 로비라운지가 높은 층에 위치한 럭셔리 호텔
-   - **주요 특징 및 후기:** 파크 하얏트 서울은 프라이빗한 분위기와 높은 서비스 퀄리티로 유명합니다. 특히, 시티뷰가 최고라는 평가와 친절한 직원분들이 인상적입니다. 또한, 룸서비스의 맛과 품격 또한 강조되며, 전망이 아름다운 호텔로 여행을 더욱 특별하게 만들어줍니다. 후기 중에는 "파크 하얏트가 진짜 제일 좋은 것"이라는 말도 있습니다.
-이 두 곳은 서울에서 럭셔리한 투숙 경험을 즐기면서 K-pop과 쇼핑을 즐기기에 적합한 장소로 추천드립니다. 즐거운 여행되세요!</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -652,39 +555,10 @@
           <t>It’s my second time in Korea, can you recommend a 3-day itinerary in Jeju to enjoy nature and traditional culture?</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>한국에서 두 번째로, 자연과 전통 문화를 즐기기 위해 제주에서 3 일간의 여정을 추천 할 수 있습니까?</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>안녕하세요! 서울을 자주 재방문하시는 여행객님! 쇼핑과 맛집 탐방을 즐기시는 여행 스타일에 어울리는 제주의 추천 장소를 소개해 드릴게요.
-1. **제주선채향**
-   - **주소:** 제주특별자치도 서귀포시 안덕면 사계남로84번길 6
-   - **AI 요약:** 맛집으로 소문난 곳
-   - **주요 특징 및 후기:** 전복죽과 칼국수가 맛있고, 사장님의 친절한 응대가 인상적이며 인기 많은 곳입니다. 하지만 대기가 있을 수 있으니 오픈런에 방문하는 것이 좋습니다. 후기에는 전복죽이 특히 맛있다는 평이 많이 나오니 맛보기 좋은 곳이에요.
-2. **제주 향토오일뱅크 미술관**
-   - **주소:** 제주특별자치도 서귀포시 안덕면 광평리 2097-20
-   - **AI 요약:** 제주의 역사와 문화를 경험할 수 있는 곳
-   - **주요 특징 및 후기:** 한국의 오일페인팅 작품을 전시하는 미술관으로, 제주의 역사와 문화를 감상할 수 있습니다. 전통적인 한국 미술을 경험하고 싶으시다면 좋은 장소입니다.
-이처럼, 맛집과 쇼핑을 즐기시는 여행객에게 매력적인 장소들을 추천해 드렸어요. 제주에서 즐거운 여행이 되시길 바라며, 즐겁고 안전한 시간 보내시길 바랍니다!</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>안녕하세요! 서울을 자주 재방문하시는 여행객님! 쇼핑과 맛집 탐방을 즐기시는 여행 스타일에 어울리는 제주의 추천 장소를 소개해 드릴게요.
-1. **제주선채향**
-   - **주소:** 제주특별자치도 서귀포시 안덕면 사계남로84번길 6
-   - **AI 요약:** 맛집으로 소문난 곳
-   - **주요 특징 및 후기:** 전복죽과 칼국수가 맛있고, 사장님의 친절한 응대가 인상적이며 인기 많은 곳입니다. 하지만 대기가 있을 수 있으니 오픈런에 방문하는 것이 좋습니다. 후기에는 전복죽이 특히 맛있다는 평이 많이 나오니 맛보기 좋은 곳이에요.
-2. **제주 향토오일뱅크 미술관**
-   - **주소:** 제주특별자치도 서귀포시 안덕면 광평리 2097-20
-   - **AI 요약:** 제주의 역사와 문화를 경험할 수 있는 곳
-   - **주요 특징 및 후기:** 한국의 오일페인팅 작품을 전시하는 미술관으로, 제주의 역사와 문화를 감상할 수 있습니다. 전통적인 한국 미술을 경험하고 싶으시다면 좋은 장소입니다.
-이처럼, 맛집과 쇼핑을 즐기시는 여행객에게 매력적인 장소들을 추천해 드렸어요. 제주에서 즐거운 여행이 되시길 바라며, 즐겁고 안전한 시간 보내시길 바랍니다!</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -700,39 +574,10 @@
           <t>We are returning visitors planning a 4-day family trip to Gangwon-do focused on food and relaxation. Any suggestions?</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>우리는 방문객들이 음식과 휴식에 중점을 둔 Gangwon-Do로 4 일 가족 여행을 계획하고 있습니다. 제안이 있습니까?</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>안녕하세요! 여행객님의 긴 체류 기간 중 방문하실 강원도에서 음식과 휴식에 중점을 둔 4일간의 가족 여행을 계획 중이시군요. 여행의 목적과 여행 스타일을 고려하여 가을에 방문하기 좋은 장소를 추천해 드리겠습니다.
-1. **허브나라농원**
-   - 주소: 강원특별자치도 평창군 봉평면 흥정계곡길 225
-   - **AI 요약**: 가성비 좋은 관광지, 힐링과 휴식을 즐길 수 있는 장소
-   - **주요 특징 및 후기**: 허브아이스크림이 맛있고, 정원과 계곡에서 시원한 휴식을 즐길 수 있으며, 공기가 맑고 아름다운 꽃 정원이 인상적입니다. 다만 가든카페에서의 서비스에 대한 후기가 있으니 참고하시기 바랍니다.
-2. **산채촌**
-   - 주소: 강원특별자치도 인제군 북면 어두원길 25
-   - **AI 요약**: 신선하고 담백한 산채정식을 즐길 수 있는 식당
-   - **주요 특징 및 후기**: 산채정식이 맛있고, 산나물과 구수한 음식을 맛볼 수 있으며, 아늑한 분위기와 넓은 내부로 가족이나 단체로 방문하기 좋습니다. 다만 가격대가 조금 높을 수 있으니 주의하셔야 합니다.
-이 두 곳은 강원도에서 음식과 휴식을 즐기기에 좋은 장소로 여행객님의 취향에 맞을 것으로 생각됩니다. 특히 가을철에 방문하시면 자연의 아름다움을 더욱 느낄 수 있을 것입니다. 즐거운 여행 되시길 바랍니다! 만약 추가 정보나 도움이 필요하시면 언제든지 물어보세요.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>안녕하세요! 여행객님의 긴 체류 기간 중 방문하실 강원도에서 음식과 휴식에 중점을 둔 4일간의 가족 여행을 계획 중이시군요. 여행의 목적과 여행 스타일을 고려하여 가을에 방문하기 좋은 장소를 추천해 드리겠습니다.
-1. **허브나라농원**
-   - 주소: 강원특별자치도 평창군 봉평면 흥정계곡길 225
-   - **AI 요약**: 가성비 좋은 관광지, 힐링과 휴식을 즐길 수 있는 장소
-   - **주요 특징 및 후기**: 허브아이스크림이 맛있고, 정원과 계곡에서 시원한 휴식을 즐길 수 있으며, 공기가 맑고 아름다운 꽃 정원이 인상적입니다. 다만 가든카페에서의 서비스에 대한 후기가 있으니 참고하시기 바랍니다.
-2. **산채촌**
-   - 주소: 강원특별자치도 인제군 북면 어두원길 25
-   - **AI 요약**: 신선하고 담백한 산채정식을 즐길 수 있는 식당
-   - **주요 특징 및 후기**: 산채정식이 맛있고, 산나물과 구수한 음식을 맛볼 수 있으며, 아늑한 분위기와 넓은 내부로 가족이나 단체로 방문하기 좋습니다. 다만 가격대가 조금 높을 수 있으니 주의하셔야 합니다.
-이 두 곳은 강원도에서 음식과 휴식을 즐기기에 좋은 장소로 여행객님의 취향에 맞을 것으로 생각됩니다. 특히 가을철에 방문하시면 자연의 아름다움을 더욱 느낄 수 있을 것입니다. 즐거운 여행 되시길 바랍니다! 만약 추가 정보나 도움이 필요하시면 언제든지 물어보세요.</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -748,39 +593,10 @@
           <t>今回は初めて韓国に旅行します。ソウルで5日間、K-popとショッピングを楽しみたいです。</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>이것은 한국으로의 첫 여행입니다. 5 일 동안 서울에서 K-Pop과 쇼핑을 즐기고 싶습니다.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>한국을 처음 방문하시는 여행객분께서는 서울에서 럭셔리한 여행을 원하시는 것으로 보입니다. 음식과 쇼핑을 즐기시는 분이시니, 다음의 두 곳을 추천해드립니다.
-1. **파크 하얏트 서울**
-   - **주소:** 서울 강남구 테헤란로 606
-   - **AI 요약:** 한달에 한번씩 꼭 가는 호텔이며 깔끔하고 고급스럽고 프라이빗한 분위기가 좋다고 합니다.
-   - **주요 특징 및 후기:** 방 크기와 뷰가 좋으며, 시티뷰와 뷔페에서의 식사가 만족스러운 곳으로 손꼽힙니다. 직원분들의 친절함과 서비스도 높게 평가받고 있습니다.
-2. **서울신라호텔 더 파크뷰**
-   - **주소:** 서울 중구 동호로 249 1층
-   - **AI 요약:** 분위기가 고급스럽고 편안한 분위기를 자랑하며, 맛있는 음식과 서비스로 유명합니다.
-   - **주요 특징 및 후기:** 음식의 맛과 서비스가 뛰어나며, 분위기가 아주 좋아 소비력이 높은 분들에게 적합한 장소입니다. 특히 디저트와 커피는 매우 인상적이라고 평가받고 있습니다.
-이 두 곳은 럭셔리한 분위기와 훌륭한 서비스로 여행을 더욱 특별하게 만들어줄 것입니다. 즐거운 여행 되시길 바랍니다!</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>한국을 처음 방문하시는 여행객분께서는 서울에서 럭셔리한 여행을 원하시는 것으로 보입니다. 음식과 쇼핑을 즐기시는 분이시니, 다음의 두 곳을 추천해드립니다.
-1. **파크 하얏트 서울**
-   - **주소:** 서울 강남구 테헤란로 606
-   - **AI 요약:** 한달에 한번씩 꼭 가는 호텔이며 깔끔하고 고급스럽고 프라이빗한 분위기가 좋다고 합니다.
-   - **주요 특징 및 후기:** 방 크기와 뷰가 좋으며, 시티뷰와 뷔페에서의 식사가 만족스러운 곳으로 손꼽힙니다. 직원분들의 친절함과 서비스도 높게 평가받고 있습니다.
-2. **서울신라호텔 더 파크뷰**
-   - **주소:** 서울 중구 동호로 249 1층
-   - **AI 요약:** 분위기가 고급스럽고 편안한 분위기를 자랑하며, 맛있는 음식과 서비스로 유명합니다.
-   - **주요 특징 및 후기:** 음식의 맛과 서비스가 뛰어나며, 분위기가 아주 좋아 소비력이 높은 분들에게 적합한 장소입니다. 특히 디저트와 커피는 매우 인상적이라고 평가받고 있습니다.
-이 두 곳은 럭셔리한 분위기와 훌륭한 서비스로 여행을 더욱 특별하게 만들어줄 것입니다. 즐거운 여행 되시길 바랍니다!</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -796,21 +612,10 @@
           <t>韓国は2回目の訪問ですが、済州島で3日間、自然と伝統文化を感じられるコースを教えてください。</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>이것은 두 번째 한국 방문이지만, 제주 섬에서 3 일 동안 자연과 전통 문화에 대한 느낌을 줄 코스에 대해 알려주십시오.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>요청하신 지역에 맞는 장소를 찾지 못했습니다.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>요청하신 지역에 맞는 장소를 찾지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -826,53 +631,20 @@
           <t>両親と一緒の再訪旅行で、江原道で4日間、美食と癒しを楽しみたいです。</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>부모님과 함께 여행을하면서 음식을 맛보고 Gangwon Province에서 휴식을 취하고 싶습니다.</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>알뜰하게 소비하는 여행객과 함께 가을에 강원도를 방문하며, 역사와 자연을 즐기고자 하는 경우, 다음의 장소들을 추천해드릴 수 있습니다:
-1. **DMZ자생식물원**
-   - **주소:** 강원특별자치도 양구군 해안면 펀치볼로 916-70
-   - **AI 요약:** 계절에 따라 즐길 수 있는 아름다운 자연 경치와 다채로운 식물들을 즐길 수 있는 곳
-   - **주요 특징 및 후기:** 
-     - "6월9일까지하는 북방계식물전시기간에 꼭 가보세요"
-     - "한번 가볼만한 곳입니다"
-     - "처음보는 꽃이 많아요"
-     - "다시 방문하고 싶은 곳입니다"
-2. **산채촌**
-   - **주소:** 강원특별자치도 인제군 북면 어두원길 25
-   - **AI 요약:** 건강한 식사와 자연을 느낄 수 있는 분위기적인 곳
-   - **주요 특징 및 후기:** 
-     - "산채정식 맛있어요"
-     - "능이 듬뿍 넣은 백숙 최고입니다"
-     - "모든게 맛있어요"
-     - "가족들과 떨어져 지내면서 밥다운 밥을 먹고 싶어서 우연히 알게되어 가보았습니다"
-이 두 곳은 강원도에서 자연을 경험하고 식사를 즐기며 가을 여행을 즐길 수 있는 좋은 장소입니다. 특히 DMZ자생식물원은 계절에 따라 변화하는 아름다운 풍경을 즐길 수 있고, 산채촌은 건강한 음식과 자연 분위기를 함께 느낄 수 있는 곳으로, 가을 힐링 여행에 적합합니다. 부모님과 함께한 여행에서 특별한 추억을 만들어보세요!</t>
+          <t>❌ 추천 실패</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>알뜰하게 소비하는 여행객과 함께 가을에 강원도를 방문하며, 역사와 자연을 즐기고자 하는 경우, 다음의 장소들을 추천해드릴 수 있습니다:
-1. **DMZ자생식물원**
-   - **주소:** 강원특별자치도 양구군 해안면 펀치볼로 916-70
-   - **AI 요약:** 계절에 따라 즐길 수 있는 아름다운 자연 경치와 다채로운 식물들을 즐길 수 있는 곳
-   - **주요 특징 및 후기:** 
-     - "6월9일까지하는 북방계식물전시기간에 꼭 가보세요"
-     - "한번 가볼만한 곳입니다"
-     - "처음보는 꽃이 많아요"
-     - "다시 방문하고 싶은 곳입니다"
-2. **산채촌**
-   - **주소:** 강원특별자치도 인제군 북면 어두원길 25
-   - **AI 요약:** 건강한 식사와 자연을 느낄 수 있는 분위기적인 곳
-   - **주요 특징 및 후기:** 
-     - "산채정식 맛있어요"
-     - "능이 듬뿍 넣은 백숙 최고입니다"
-     - "모든게 맛있어요"
-     - "가족들과 떨어져 지내면서 밥다운 밥을 먹고 싶어서 우연히 알게되어 가보았습니다"
-이 두 곳은 강원도에서 자연을 경험하고 식사를 즐기며 가을 여행을 즐길 수 있는 좋은 장소입니다. 특히 DMZ자생식물원은 계절에 따라 변화하는 아름다운 풍경을 즐길 수 있고, 산채촌은 건강한 음식과 자연 분위기를 함께 느낄 수 있는 곳으로, 가을 힐링 여행에 적합합니다. 부모님과 함께한 여행에서 특별한 추억을 만들어보세요!</t>
+          <t>❌ 추천 실패</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ja</t>
         </is>
       </c>
     </row>
@@ -890,39 +662,10 @@
           <t>这是我第一次去韩国，计划在首尔待5天，主要是K-pop和购物，有什么推荐？</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>한국에가는 것은 이번이 처음입니다. 나는 주로 K-pop과 쇼핑을 5 일 동안 서울에 머물 계획이다. 권장 사항이 있습니까?</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>한국을 처음 방문하여 K-pop과 쇼핑을 즐기는 럭셔리 여행객을 위한 추천 장소는 다음과 같습니다:
-1. **서울신라호텔 더 파크뷰**
-   - **주소:** 서울 중구 동호로 249 1층
-   - **AI 요약:** 분위기고급스러운, 맛신선한 음식, 고소하고 달콤한 맛을 즐길 수 있는 곳으로, 가족이나 연인과 함께하는 기념일이나 데이트에 적합합니다.
-   - **주요 특징 및 후기:** 음식의 맛과 서비스, 분위기가 뛰어나며, 특히 디저트와 커피가 매우 좋게 평가되었습니다. 뷔페를 좋아하지 않는 분들도 만족할 만한 곳으로, 비싼 가격에도 불구하고 가치 있는 경험이라고 할 수 있습니다.
-2. **파크 하얏트 서울**
-   - **주소:** 서울 강남구 테헤란로 606
-   - **AI 요약:** 깔끔하고 고급스러운 분위기, 서비스와 뷰가 뛰어난 곳으로, 가성비는 높지만 특별한 경험을 원하는 분들에게 추천합니다.
-   - **주요 특징 및 후기:** 고급스러운 분위기와 친절한 직원들이 인상적이며, 시티뷰가 훌륭한 곳으로 평가되었습니다. 룸서비스도 맛있고, 조식도 훌륭하다고 소문이 난 호텔입니다.
-이 두 곳은 서울에서 럭셔리한 여행을 즐기고자 하는 여행객들에게 적합한 장소입니다. 둘 다 음식, 서비스, 분위기 등에서 뛰어난 평가를 받고 있으며, 특히 K-pop과 쇼핑을 즐기는 분들께 좋은 추억을 선사할 것입니다. 즐거운 여행이 되시길 바랍니다!</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>한국을 처음 방문하여 K-pop과 쇼핑을 즐기는 럭셔리 여행객을 위한 추천 장소는 다음과 같습니다:
-1. **서울신라호텔 더 파크뷰**
-   - **주소:** 서울 중구 동호로 249 1층
-   - **AI 요약:** 분위기고급스러운, 맛신선한 음식, 고소하고 달콤한 맛을 즐길 수 있는 곳으로, 가족이나 연인과 함께하는 기념일이나 데이트에 적합합니다.
-   - **주요 특징 및 후기:** 음식의 맛과 서비스, 분위기가 뛰어나며, 특히 디저트와 커피가 매우 좋게 평가되었습니다. 뷔페를 좋아하지 않는 분들도 만족할 만한 곳으로, 비싼 가격에도 불구하고 가치 있는 경험이라고 할 수 있습니다.
-2. **파크 하얏트 서울**
-   - **주소:** 서울 강남구 테헤란로 606
-   - **AI 요약:** 깔끔하고 고급스러운 분위기, 서비스와 뷰가 뛰어난 곳으로, 가성비는 높지만 특별한 경험을 원하는 분들에게 추천합니다.
-   - **주요 특징 및 후기:** 고급스러운 분위기와 친절한 직원들이 인상적이며, 시티뷰가 훌륭한 곳으로 평가되었습니다. 룸서비스도 맛있고, 조식도 훌륭하다고 소문이 난 호텔입니다.
-이 두 곳은 서울에서 럭셔리한 여행을 즐기고자 하는 여행객들에게 적합한 장소입니다. 둘 다 음식, 서비스, 분위기 등에서 뛰어난 평가를 받고 있으며, 특히 K-pop과 쇼핑을 즐기는 분들께 좋은 추억을 선사할 것입니다. 즐거운 여행이 되시길 바랍니다!</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -938,21 +681,10 @@
           <t>这是我第二次来韩国，请推荐在济州岛3天能欣赏自然风光和体验传统文化的行程。</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>이것은 한국에서 두 번째입니다. 자연 경관을 즐기고 3 일 동안 제주 섬의 전통 문화를 경험하기 위해 여행을 추천하십시오.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>요청하신 지역에 맞는 장소를 찾지 못했습니다.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>요청하신 지역에 맞는 장소를 찾지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -968,39 +700,10 @@
           <t>我和父母是再次来访韩国，想在江原道玩4天，以美食和放松为主，有什么建议？</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>부모님과 저는 다시 한국을 방문하고 4 일 동안 Gangwon에서 음식과 휴식에 중점을두고 싶어합니다. 어떤 제안이 있습니까?</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>알뜰하게 소비하는 특징을 가진 여행객이 한국을 재방문하여 강원도에서 4일간의 여행을 즐길 때, '산채촌'과 '달구새끼'를 추천드립니다.
-1. **산채촌**
-   - **주소:** 강원특별자치도 인제군 북면 어두원길 25
-   - **AI 요약:** 분위기 자연 경관, 건강한 식사를 즐기기 좋은 곳, 맛있는 산채정식과 더덕구이가 유명합니다. 가족이나 연인과 함께 즐기기 좋습니다.
-   - **주요 특징 및 후기:** "산채정식 맛있어요", "능이 듬뿍 넣은 백숙 최고입니다", "더덕구이 맛있음" 등의 실제 후기가 있습니다. 이곳은 맛과 인심이 최고로 평가받는 곳으로, 가족과 함께 건강하고 맛있는 식사를 즐길 수 있는 장소입니다.
-2. **달구새끼**
-   - **주소:** 강원특별자치도 홍천군 북방면 홍천로 57-12 1층
-   - **AI 요약:** 전통적이고 아늑한 분위기, 가족 단위 식사나 모임에 적합, 대한민국 닭갈비 중 최고로 평가됨. 연탄불향이 좋고 맛있는 음식 제공.
-   - **주요 특징 및 후기:** "연탄닭갈비 맛있어요", "꼭 가보셨으면 좋겠어요", "꼭 한번 가보세요" 등의 후기가 있습니다. 이곳은 맛과 서비스가 뛰어나며, 가족이나 연인과 함께 식사를 즐기기에 좋은 곳입니다.
-이 두 장소는 알뜰하게 소비하는 여행객이 한국을 즐기는 데에 적합하며, 강원도에서 가을 풍경과 맛있는 음식을 경험할 수 있는 좋은 선택일 것입니다. 즐거운 여행 되시길 바랍니다!</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>알뜰하게 소비하는 특징을 가진 여행객이 한국을 재방문하여 강원도에서 4일간의 여행을 즐길 때, '산채촌'과 '달구새끼'를 추천드립니다.
-1. **산채촌**
-   - **주소:** 강원특별자치도 인제군 북면 어두원길 25
-   - **AI 요약:** 분위기 자연 경관, 건강한 식사를 즐기기 좋은 곳, 맛있는 산채정식과 더덕구이가 유명합니다. 가족이나 연인과 함께 즐기기 좋습니다.
-   - **주요 특징 및 후기:** "산채정식 맛있어요", "능이 듬뿍 넣은 백숙 최고입니다", "더덕구이 맛있음" 등의 실제 후기가 있습니다. 이곳은 맛과 인심이 최고로 평가받는 곳으로, 가족과 함께 건강하고 맛있는 식사를 즐길 수 있는 장소입니다.
-2. **달구새끼**
-   - **주소:** 강원특별자치도 홍천군 북방면 홍천로 57-12 1층
-   - **AI 요약:** 전통적이고 아늑한 분위기, 가족 단위 식사나 모임에 적합, 대한민국 닭갈비 중 최고로 평가됨. 연탄불향이 좋고 맛있는 음식 제공.
-   - **주요 특징 및 후기:** "연탄닭갈비 맛있어요", "꼭 가보셨으면 좋겠어요", "꼭 한번 가보세요" 등의 후기가 있습니다. 이곳은 맛과 서비스가 뛰어나며, 가족이나 연인과 함께 식사를 즐기기에 좋은 곳입니다.
-이 두 장소는 알뜰하게 소비하는 여행객이 한국을 즐기는 데에 적합하며, 강원도에서 가을 풍경과 맛있는 음식을 경험할 수 있는 좋은 선택일 것입니다. 즐거운 여행 되시길 바랍니다!</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1016,39 +719,10 @@
           <t>Das ist meine erste Reise nach Korea. Ich plane 5 Tage in Seoul mit Schwerpunkt K-pop und Shopping. Wohin soll ich gehen?</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>이것은 한국으로의 첫 여행입니다. 나는 K-pop과 쇼핑에 중점을 둔 서울에서 5 일을 계획합니다. 어디로 가야합니까?</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>여행객님, 한국을 처음 방문하시는 여행객이신 것으로 알고 있습니다. 서울에서 K-pop과 쇼핑을 중점으로 즐기실 예정이라고 하셨네요. 그런 여행 스타일에 가장 적합한 장소를 추천해드리겠습니다.
-1. **서울신라호텔 더 파크뷰**
-   - 주소: 서울 중구 동호로 249 1층
-   - **AI 요약**: 분위기고급스러운, 맛신선한 뷔페로 유명한 곳입니다. 방문 목적이 기념일이라면 특히 추천합니다.
-   - **주요 특징 및 후기**: 음식의 맛과 서비스가 최고 수준이며, 특히 디저트와 커피는 극찬을 받는 편입니다. 뷔페를 좋아하지 않는 분들도 만족할 만한 곳으로 손꼽히고 있습니다.
-2. **시그니엘 서울**
-   - 주소: 서울 송파구 올림픽로 300 롯데월드타워 76~101층
-   - **AI 요약**: 서울을 상징하는 건물인 롯데월드타워에 위치한 호텔로, 높은 층에서 파노라마 시티뷰를 감상할 수 있습니다.
-   - **주요 특징 및 후기**: 고급스러운 분위기와 훌륭한 조식 등이 호평을 받고 있습니다. 서울시내야경을 감상하면서 여행의 피로를 풀기에 안성맞춤인 곳입니다.
-이 두 곳은 서울에서 럭셔리한 여행을 즐기시는 분께 추천드리는 장소입니다. 특히 서울신라호텔 더 파크뷰는 맛있는 음식과 고급스러운 분위기로 기념일이나 특별한 날에 방문하기 좋은 곳이며, 시그니엘 서울은 높은 층에서 서울의 아름다운 야경을 감상할 수 있는 호텔입니다. 즐거운 여행 되시길 바랍니다!</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>여행객님, 한국을 처음 방문하시는 여행객이신 것으로 알고 있습니다. 서울에서 K-pop과 쇼핑을 중점으로 즐기실 예정이라고 하셨네요. 그런 여행 스타일에 가장 적합한 장소를 추천해드리겠습니다.
-1. **서울신라호텔 더 파크뷰**
-   - 주소: 서울 중구 동호로 249 1층
-   - **AI 요약**: 분위기고급스러운, 맛신선한 뷔페로 유명한 곳입니다. 방문 목적이 기념일이라면 특히 추천합니다.
-   - **주요 특징 및 후기**: 음식의 맛과 서비스가 최고 수준이며, 특히 디저트와 커피는 극찬을 받는 편입니다. 뷔페를 좋아하지 않는 분들도 만족할 만한 곳으로 손꼽히고 있습니다.
-2. **시그니엘 서울**
-   - 주소: 서울 송파구 올림픽로 300 롯데월드타워 76~101층
-   - **AI 요약**: 서울을 상징하는 건물인 롯데월드타워에 위치한 호텔로, 높은 층에서 파노라마 시티뷰를 감상할 수 있습니다.
-   - **주요 특징 및 후기**: 고급스러운 분위기와 훌륭한 조식 등이 호평을 받고 있습니다. 서울시내야경을 감상하면서 여행의 피로를 풀기에 안성맞춤인 곳입니다.
-이 두 곳은 서울에서 럭셔리한 여행을 즐기시는 분께 추천드리는 장소입니다. 특히 서울신라호텔 더 파크뷰는 맛있는 음식과 고급스러운 분위기로 기념일이나 특별한 날에 방문하기 좋은 곳이며, 시그니엘 서울은 높은 층에서 서울의 아름다운 야경을 감상할 수 있는 호텔입니다. 즐거운 여행 되시길 바랍니다!</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1064,21 +738,10 @@
           <t>Ich besuche Korea zum zweiten Mal. Empfehlen Sie eine 3-tägige Route auf Jeju für Natur und traditionelle Kultur.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>두 번째로 한국을 방문합니다. 자연과 전통 문화를 위해 Jeju에서 3 일간의 경로를 추천하십시오.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>요청하신 지역에 맞는 장소를 찾지 못했습니다.</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>요청하신 지역에 맞는 장소를 찾지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1094,39 +757,10 @@
           <t>Wir sind Wiederholungsbesucher und planen eine 4-tägige Familienreise nach Gangwon-do mit Schwerpunkt auf Essen und Entspannung.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>우리는 반복 방문자이며 음식과 휴식에 중점을 둔 Gangwon-Do로 4 일 가족 여행을 계획합니다.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>알뜰한 소비와 음식, 휴식을 중요시하는 여행객을 위한 강원도 여행 추천을 해드릴게요. 
-1. **허브나라농원**
-   - **주소:** 강원특별자치도 평창군 봉평면 흥정계곡길 225
-   - **AI 요약:** 가성비 좋은 관광지로, 헛걸음 방지를 위해 체크 필수
-   - **주요 특징 및 후기:** 허브나라농원은 가격 대비 가성비가 뛰어나며, 특히 허브아이스크림이 맛있는 곳으로 소개됩니다. 또한, 정원과 계곡에서의 휴식을 즐길 수 있어 힐링하기에 좋은 장소입니다. 다만, 가든카페가 불친절하다는 후기도 있지만, 노력이 보이는 공간이라는 얘기도 있습니다.
-2. **평창문화예술단지**
-   - **주소:** 강원도 평창군 진부면 봉평로 253
-   - **AI 요약:** 자연과 문화가 조화를 이룬 아름다운 공간
-   - **주요 특징 및 후기:** 평창문화예술단지는 자연과 문화가 어우러진 아름다운 장소로 소개됩니다. 전통가옥과 현대적 건축물이 공존하며, 예술 전시와 공연을 즐길 수 있는 곳입니다. 여유로운 분위기와 아름다운 풍경이 인상적이라는 후기가 많습니다.
-이 여행객에게 허브나라농원과 평창문화예술단지는 가을 강원도 여행을 즐기기에 적합한 장소일 것입니다. 각 장소의 특징과 후기를 참고하여 즐거운 여행이 되시길 바랍니다!</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>알뜰한 소비와 음식, 휴식을 중요시하는 여행객을 위한 강원도 여행 추천을 해드릴게요. 
-1. **허브나라농원**
-   - **주소:** 강원특별자치도 평창군 봉평면 흥정계곡길 225
-   - **AI 요약:** 가성비 좋은 관광지로, 헛걸음 방지를 위해 체크 필수
-   - **주요 특징 및 후기:** 허브나라농원은 가격 대비 가성비가 뛰어나며, 특히 허브아이스크림이 맛있는 곳으로 소개됩니다. 또한, 정원과 계곡에서의 휴식을 즐길 수 있어 힐링하기에 좋은 장소입니다. 다만, 가든카페가 불친절하다는 후기도 있지만, 노력이 보이는 공간이라는 얘기도 있습니다.
-2. **평창문화예술단지**
-   - **주소:** 강원도 평창군 진부면 봉평로 253
-   - **AI 요약:** 자연과 문화가 조화를 이룬 아름다운 공간
-   - **주요 특징 및 후기:** 평창문화예술단지는 자연과 문화가 어우러진 아름다운 장소로 소개됩니다. 전통가옥과 현대적 건축물이 공존하며, 예술 전시와 공연을 즐길 수 있는 곳입니다. 여유로운 분위기와 아름다운 풍경이 인상적이라는 후기가 많습니다.
-이 여행객에게 허브나라농원과 평창문화예술단지는 가을 강원도 여행을 즐기기에 적합한 장소일 것입니다. 각 장소의 특징과 후기를 참고하여 즐거운 여행이 되시길 바랍니다!</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1142,39 +776,10 @@
           <t>C’est mon premier voyage en Corée : je prévois 5 jours à Séoul axés sur le K-pop et le shopping. Où devrais-je aller ?</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>이것은 한국으로의 첫 여행입니다. 나는 K-pop과 쇼핑에 중점을 둔 서울에서 5 일을 계획하고 있습니다. 어디로 가야합니까?</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>안녕하세요! 한국을 처음 방문하는 여행객님께서는 서울에서 K-pop과 쇼핑을 중심으로 5일간의 여행을 계획 중이시군요. 이러한 취향을 고려하여 여행을 즐기기 좋은 장소를 추천해드리겠습니다.
-1. **서울신라호텔 더 파크뷰**
-   - **주소:** 서울 중구 동호로 249 1층
-   - **AI 요약:** 분위기고급스러운 호텔로, 맛있는 음식과 훌륭한 서비스로 유명합니다. 연인 데이트나 기념일에 적합한 곳입니다.
-   - **주요 특징 및 후기:** 음식의 맛과 품질이 뛰어나며, 호텔다운 서비스와 분위기로 손님들을 매료시킵니다. 고객 후기에서는 디저트와 커피의 맛을 칭찬하는 내용이 많이 나오고 있습니다.
-2. **시그니엘 서울**
-   - **주소:** 서울 송파구 올림픽로 300 롯데월드타워 76~101층
-   - **AI 요약:** 높은 층에서 서울시내의 아름다운 야경을 감상할 수 있는 호텔로, 조식과 서비스가 인상적입니다.
-   - **주요 특징 및 후기:** 높은 층에서 파노라마처럼 펼쳐지는 서울 야경을 즐길 수 있으며, 조식과 웰컴티 서비스 등이 좋은 평가를 받고 있습니다.
-이 두 곳은 숙박 시 고급스러운 분위기와 훌륭한 서비스를 경험할 수 있을 뿐만 아니라, 서울의 도심지에 위치하여 쇼핑이나 관광지 방문에도 편리한 위치에 있습니다. K-pop과 쇼핑을 즐기는 여행에 적합한 곳이니 참고해보시기 바랍니다. 즐거운 여행 되시길 바라겠습니다!</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>안녕하세요! 한국을 처음 방문하는 여행객님께서는 서울에서 K-pop과 쇼핑을 중심으로 5일간의 여행을 계획 중이시군요. 이러한 취향을 고려하여 여행을 즐기기 좋은 장소를 추천해드리겠습니다.
-1. **서울신라호텔 더 파크뷰**
-   - **주소:** 서울 중구 동호로 249 1층
-   - **AI 요약:** 분위기고급스러운 호텔로, 맛있는 음식과 훌륭한 서비스로 유명합니다. 연인 데이트나 기념일에 적합한 곳입니다.
-   - **주요 특징 및 후기:** 음식의 맛과 품질이 뛰어나며, 호텔다운 서비스와 분위기로 손님들을 매료시킵니다. 고객 후기에서는 디저트와 커피의 맛을 칭찬하는 내용이 많이 나오고 있습니다.
-2. **시그니엘 서울**
-   - **주소:** 서울 송파구 올림픽로 300 롯데월드타워 76~101층
-   - **AI 요약:** 높은 층에서 서울시내의 아름다운 야경을 감상할 수 있는 호텔로, 조식과 서비스가 인상적입니다.
-   - **주요 특징 및 후기:** 높은 층에서 파노라마처럼 펼쳐지는 서울 야경을 즐길 수 있으며, 조식과 웰컴티 서비스 등이 좋은 평가를 받고 있습니다.
-이 두 곳은 숙박 시 고급스러운 분위기와 훌륭한 서비스를 경험할 수 있을 뿐만 아니라, 서울의 도심지에 위치하여 쇼핑이나 관광지 방문에도 편리한 위치에 있습니다. K-pop과 쇼핑을 즐기는 여행에 적합한 곳이니 참고해보시기 바랍니다. 즐거운 여행 되시길 바라겠습니다!</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1190,21 +795,10 @@
           <t>C’est ma deuxième visite en Corée : recommandez un itinéraire de 3 jours à Jeju pour profiter de la nature et de la culture traditionnelle.</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>이것은 한국을 두 번째로 방문하는 것입니다. 자연과 전통 문화를 즐기기 위해 제주로가는 3 일간의 경로를 추천합니다.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>요청하신 지역에 맞는 장소를 찾지 못했습니다.</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>요청하신 지역에 맞는 장소를 찾지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1220,39 +814,10 @@
           <t>Nous sommes des visiteurs réguliers et faisons un voyage en famille de 4 jours à Gangwon-do axé sur la gastronomie et la détente.</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>우리는 정기적 인 방문객이며 미식과 휴식에 중점을 둔 Gangwon-Do로 4 일 가족 여행을합니다.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>안녕하세요! 문화, 역사, 자연 탐방을 주목적으로 가을에 한국을 재방문하는 여행객을 위한 추천 장소를 소개해 드릴게요.
-1. **허브나라농원**
-   - **주소:** 강원특별자치도 평창군 봉평면 흥정계곡길 225
-   - **AI 요약:** 허브와 꽃이 가득한 아름다운 정원으로, 힐링과 자연 즐기기에 최적의 장소입니다.
-   - **주요 특징 및 후기:** 허브아이스크림과 힐링을 즐길 수 있는 계곡까지 이어지는 아름다운 정원으로 가성비 좋은 관광지이며, 가격 대비 경치와 시설이 좋은 편입니다. 또한, 공기 맑은 곳에서 산책과 허브차를 마시며 휴식하기 좋습니다.
-2. **강릉선교장**
-   - **주소:** 강원특별자치도 강릉시 운정길 63
-   - **AI 요약:** 관동 풍류를 느낄 수 있는 한옥 선교장으로, 고즈넉한 분위기와 역사적인 가치를 느낄 수 있습니다.
-   - **주요 특징 및 후기:** 사진스팟이 많고, 관동 풍류의 길을 따라 산책할 수 있는 곳으로, 입장료가 아깝지 않을 정도로 다양한 볼거리가 있습니다. 또한, 친절한 직원들과 함께 조용한 분위기 속에서 즐길 수 있는 좋은 장소입니다.
-이러한 장소들은 문화, 역사, 자연을 경험하며 소비를 알뜰하게 할 수 있는 여행객에게 적합한 장소입니다. 각각의 장소에서 특별한 경험을 즐기며 가을 강원도 여행을 더욱 풍성하게 만들어보세요. 즐거운 여행 되세요!</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>안녕하세요! 문화, 역사, 자연 탐방을 주목적으로 가을에 한국을 재방문하는 여행객을 위한 추천 장소를 소개해 드릴게요.
-1. **허브나라농원**
-   - **주소:** 강원특별자치도 평창군 봉평면 흥정계곡길 225
-   - **AI 요약:** 허브와 꽃이 가득한 아름다운 정원으로, 힐링과 자연 즐기기에 최적의 장소입니다.
-   - **주요 특징 및 후기:** 허브아이스크림과 힐링을 즐길 수 있는 계곡까지 이어지는 아름다운 정원으로 가성비 좋은 관광지이며, 가격 대비 경치와 시설이 좋은 편입니다. 또한, 공기 맑은 곳에서 산책과 허브차를 마시며 휴식하기 좋습니다.
-2. **강릉선교장**
-   - **주소:** 강원특별자치도 강릉시 운정길 63
-   - **AI 요약:** 관동 풍류를 느낄 수 있는 한옥 선교장으로, 고즈넉한 분위기와 역사적인 가치를 느낄 수 있습니다.
-   - **주요 특징 및 후기:** 사진스팟이 많고, 관동 풍류의 길을 따라 산책할 수 있는 곳으로, 입장료가 아깝지 않을 정도로 다양한 볼거리가 있습니다. 또한, 친절한 직원들과 함께 조용한 분위기 속에서 즐길 수 있는 좋은 장소입니다.
-이러한 장소들은 문화, 역사, 자연을 경험하며 소비를 알뜰하게 할 수 있는 여행객에게 적합한 장소입니다. 각각의 장소에서 특별한 경험을 즐기며 가을 강원도 여행을 더욱 풍성하게 만들어보세요. 즐거운 여행 되세요!</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1268,39 +833,10 @@
           <t>Este es mi primer viaje a Corea, planeo quedarme 5 días en Seúl centrado en K-pop y compras. ¿Dónde debería ir?</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>이것은 한국으로의 첫 여행입니다. 저는 K-Pop과 구매에 중점을 둔 서울에서 5 일을 머물려고합니다. 어디로 가야합니까?</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>한국을 처음 방문하시는 K-pop과 쇼핑을 즐기는 럭셔리 여행객을 위한 추천 장소입니다.
-1. **서울신라호텔 더 파크뷰**
-   - **주소:** 서울 중구 동호로 249 1층
-   - **AI 요약:** 분위기 고급스러운 호텔로, 맛있는 음식과 서비스로 유명합니다. 주로 기념일이나 데이트에 적합한 곳으로 소개되며, 디저트와 커피가 매우 맛있는 곳입니다.
-   - **주요 특징 및 후기:** 고급스러운 분위기와 서비스로 호평을 받는 호텔이며, 음식의 맛과 품질이 뛰어나다는 후기가 많습니다. 특히, 신선하고 다채로운 메뉴로 손님들을 매료시키는데, 커피와 디저트도 강조되는 곳입니다.
-2. **시그니엘 서울**
-   - **주소:** 서울 송파구 올림픽로 300 롯데월드타워 76~101층
-   - **AI 요약:** 서울을 상징하는 건물인 시그니엘은 뷰가 최고로 유명합니다. 높은 층에서의 파노라마 시티 뷰를 즐길 수 있으며, 조식과 웰컴 티서비스 등이 좋은 평가를 받고 있습니다.
-   - **주요 특징 및 후기:** 서울의 랜드마크인 롯데월드타워에 위치한 시그니엘은 최고의 파노라마 뷰를 자랑하며, 조식과 서비스에 대한 호평이 많이 올라오는 곳입니다. 고급스러운 분위기와 편안한 감성을 선사하는 호텔로, 특히 뷰가 인상적이라는 평가가 많습니다.
-이 두 곳은 럭셔리한 분위기와 훌륭한 서비스로 유명하며, 특히 음식과 뷰에 대한 만족도가 높은 곳입니다. K-pop과 쇼핑을 즐기는 여행객에게 특히 적합한 장소로 추천드립니다. 각각의 곳에서 멋진 시간을 보내시길 바랍니다!</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>한국을 처음 방문하시는 K-pop과 쇼핑을 즐기는 럭셔리 여행객을 위한 추천 장소입니다.
-1. **서울신라호텔 더 파크뷰**
-   - **주소:** 서울 중구 동호로 249 1층
-   - **AI 요약:** 분위기 고급스러운 호텔로, 맛있는 음식과 서비스로 유명합니다. 주로 기념일이나 데이트에 적합한 곳으로 소개되며, 디저트와 커피가 매우 맛있는 곳입니다.
-   - **주요 특징 및 후기:** 고급스러운 분위기와 서비스로 호평을 받는 호텔이며, 음식의 맛과 품질이 뛰어나다는 후기가 많습니다. 특히, 신선하고 다채로운 메뉴로 손님들을 매료시키는데, 커피와 디저트도 강조되는 곳입니다.
-2. **시그니엘 서울**
-   - **주소:** 서울 송파구 올림픽로 300 롯데월드타워 76~101층
-   - **AI 요약:** 서울을 상징하는 건물인 시그니엘은 뷰가 최고로 유명합니다. 높은 층에서의 파노라마 시티 뷰를 즐길 수 있으며, 조식과 웰컴 티서비스 등이 좋은 평가를 받고 있습니다.
-   - **주요 특징 및 후기:** 서울의 랜드마크인 롯데월드타워에 위치한 시그니엘은 최고의 파노라마 뷰를 자랑하며, 조식과 서비스에 대한 호평이 많이 올라오는 곳입니다. 고급스러운 분위기와 편안한 감성을 선사하는 호텔로, 특히 뷰가 인상적이라는 평가가 많습니다.
-이 두 곳은 럭셔리한 분위기와 훌륭한 서비스로 유명하며, 특히 음식과 뷰에 대한 만족도가 높은 곳입니다. K-pop과 쇼핑을 즐기는 여행객에게 특히 적합한 장소로 추천드립니다. 각각의 곳에서 멋진 시간을 보내시길 바랍니다!</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1316,21 +852,10 @@
           <t>Es mi segunda vez en Corea, recomiéndame un itinerario de 3 días en Jeju para disfrutar de la naturaleza y la cultura tradicional.</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>한국에서 두 번째로, 나는 전통적인 자연과 문화를 즐기기 위해 Jeju의 3 일간의 여정을 추천합니다.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>요청하신 지역에 맞는 장소를 찾지 못했습니다.</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>요청하신 지역에 맞는 장소를 찾지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1346,39 +871,10 @@
           <t>Somos visitantes recurrentes y planeamos un viaje familiar de 4 días a Gangwon-do centrado en comida y relajación. ¿Alguna sugerencia?</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>우리는 반복적 인 방문객이며 음식과 휴식에 중점을 둔 Gangwon-Do로 4 일 가족 여행을 계획하고 있습니다. 제안이 있습니까?</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>안녕하세요! 여행 목적이 쇼핑과 맛집 탐방인 여행객을 위한 강원도 속초의 추천 장소입니다.
-1. **전원식당**
-   - 주소: 강원특별자치도 속초시 영금정로 15 1층
-   - AI 요약: 분위기정갈한 로컬 맛집으로, 매콤하고 달달한 음식을 즐길 수 있습니다. 가격도 저렴하며, 웨이팅 없이 식사 가능합니다.
-   - 주요 특징 및 후기: "고기가 두툼하고 맛있고, 김치찜 느낌이어서 밥도둑입니다. 해산물 질릴 때 드시면 좋고, 두루치기가 유명한 곳으로 명성이 있습니다."
-2. **해질녘**
-   - 주소: 강원도 속초시 영랑해안길 23
-   - AI 요약: 해안가에 위치한 횟집으로, 신선한 해산물과 감각적인 분위기를 즐길 수 있습니다. 가족 및 커플 모임에 적합합니다.
-   - 주요 특징 및 후기: "해산물이 신선하고 맛있어서, 특히 회가 매우 신선하고 식감이 좋습니다. 뷰가 아름다워 특별한 날에 추천합니다."
-이 두 곳은 여행객의 쇼핑과 미식에 집중하는 여행 스타일과 가족 여행에 적합한 분위기를 고려하여 추천드립니다. 즐거운 여행되세요!</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>안녕하세요! 여행 목적이 쇼핑과 맛집 탐방인 여행객을 위한 강원도 속초의 추천 장소입니다.
-1. **전원식당**
-   - 주소: 강원특별자치도 속초시 영금정로 15 1층
-   - AI 요약: 분위기정갈한 로컬 맛집으로, 매콤하고 달달한 음식을 즐길 수 있습니다. 가격도 저렴하며, 웨이팅 없이 식사 가능합니다.
-   - 주요 특징 및 후기: "고기가 두툼하고 맛있고, 김치찜 느낌이어서 밥도둑입니다. 해산물 질릴 때 드시면 좋고, 두루치기가 유명한 곳으로 명성이 있습니다."
-2. **해질녘**
-   - 주소: 강원도 속초시 영랑해안길 23
-   - AI 요약: 해안가에 위치한 횟집으로, 신선한 해산물과 감각적인 분위기를 즐길 수 있습니다. 가족 및 커플 모임에 적합합니다.
-   - 주요 특징 및 후기: "해산물이 신선하고 맛있어서, 특히 회가 매우 신선하고 식감이 좋습니다. 뷰가 아름다워 특별한 날에 추천합니다."
-이 두 곳은 여행객의 쇼핑과 미식에 집중하는 여행 스타일과 가족 여행에 적합한 분위기를 고려하여 추천드립니다. 즐거운 여행되세요!</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
